--- a/model_outputs_paper1/TASK_B_LOS/metrics_LOS_3class.xlsx
+++ b/model_outputs_paper1/TASK_B_LOS/metrics_LOS_3class.xlsx
@@ -485,169 +485,169 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5849056603773585</v>
+        <v>0.5220125786163522</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5786553348129703</v>
+        <v>0.5102356592504376</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5782148620192968</v>
+        <v>0.4953668575107493</v>
       </c>
       <c r="D2" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
         <v>14</v>
       </c>
       <c r="F2" t="n">
+        <v>23</v>
+      </c>
+      <c r="G2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" t="n">
+        <v>31</v>
+      </c>
+      <c r="I2" t="n">
         <v>12</v>
       </c>
-      <c r="G2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I2" t="n">
-        <v>14</v>
-      </c>
       <c r="J2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
         <v>40</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>ExtraTrees</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.5786163522012578</v>
+        <v>0.4842767295597484</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5794853750518775</v>
+        <v>0.4688780021292336</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5751166493269019</v>
+        <v>0.444487932159165</v>
       </c>
       <c r="D3" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="G3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>RandomForest</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.5786163522012578</v>
+        <v>0.4654088050314465</v>
       </c>
       <c r="B4" t="n">
-        <v>0.5785786463126364</v>
+        <v>0.4607445100055938</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5779518166430848</v>
+        <v>0.4591493235182704</v>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I4" t="n">
         <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K4" t="n">
         <v>10</v>
       </c>
       <c r="L4" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>LightGBM</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.559748427672956</v>
+        <v>0.4654088050314465</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5589554124036883</v>
+        <v>0.4608663093884768</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5584853754265828</v>
+        <v>0.4611349490291166</v>
       </c>
       <c r="D5" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I5" t="n">
         <v>13</v>
       </c>
       <c r="J5" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -657,44 +657,44 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.5471698113207547</v>
+        <v>0.4528301886792453</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5462837654955882</v>
+        <v>0.4493720565149137</v>
       </c>
       <c r="C6" t="n">
-        <v>0.545774475533328</v>
+        <v>0.4500704307718908</v>
       </c>
       <c r="D6" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E6" t="n">
         <v>13</v>
       </c>
       <c r="F6" t="n">
+        <v>18</v>
+      </c>
+      <c r="G6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I6" t="n">
+        <v>13</v>
+      </c>
+      <c r="J6" t="n">
+        <v>18</v>
+      </c>
+      <c r="K6" t="n">
         <v>11</v>
       </c>
-      <c r="G6" t="n">
-        <v>10</v>
-      </c>
-      <c r="H6" t="n">
-        <v>30</v>
-      </c>
-      <c r="I6" t="n">
-        <v>12</v>
-      </c>
-      <c r="J6" t="n">
-        <v>14</v>
-      </c>
-      <c r="K6" t="n">
-        <v>12</v>
-      </c>
       <c r="L6" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ExtraTrees</t>
+          <t>XGBoost</t>
         </is>
       </c>
     </row>
